--- a/submissions/excel/excel_07_february_close.xlsx
+++ b/submissions/excel/excel_07_february_close.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\venti\Downloads\idynamics-training\idynamics-analyst-training\submissions\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F55E740-4ACF-4F34-A7E0-98D573ACD872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5298B7B-16B9-4F5C-942D-3F127F2F7E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Historical Baseline" sheetId="1" r:id="rId1"/>
     <sheet name="Forecast Assumptions" sheetId="2" r:id="rId2"/>
-    <sheet name="2026 Forecast" sheetId="3" r:id="rId3"/>
-    <sheet name="Jan 2026 A vs F " sheetId="9" r:id="rId4"/>
+    <sheet name="Jan 2026 A vs F " sheetId="9" r:id="rId3"/>
+    <sheet name="2026 Forecast" sheetId="3" r:id="rId4"/>
     <sheet name="Feb 2026 A vs F" sheetId="12" r:id="rId5"/>
     <sheet name="KPI Tracker" sheetId="10" r:id="rId6"/>
     <sheet name="Waterfall Data" sheetId="11" r:id="rId7"/>
@@ -1160,24 +1160,6 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={DABA5F44-B889-496F-A0C1-7D24F3B228AF}</author>
-  </authors>
-  <commentList>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{DABA5F44-B889-496F-A0C1-7D24F3B228AF}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    The Jan 2026 A vs F file does not include Contraction MRR</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
     <author>Michael Bezrukov</author>
   </authors>
   <commentList>
@@ -1349,7 +1331,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="677">
   <si>
     <t>HISTORICAL BASELINE — 2024 &amp; 2025 ACTUALS</t>
   </si>
@@ -3370,14 +3352,23 @@
     <t xml:space="preserve">The churn of $594 was subscription based, not customer based. This means that the only reduction was in the tier of subscription or seats, no accounts were lost. This is significantly better as not only did we gain 2 new accounts, we can recover the subscription churn with a potential upsell in the future. </t>
   </si>
   <si>
-    <t xml:space="preserve">All of the OpEx lines were the same as expectation and the variance in COGS is due to the increase in revenue meaning it is mechanical and expected. </t>
+    <t>OpEx ran $1000 more than anticipated. The revenue beat was partially offset by the overrun in costs and the variance in COGS is due to the increase in revenue meaning it is mechanical and expected.  Overall, this leaves a EBITDA beat of $235</t>
+  </si>
+  <si>
+    <t>Jan 2026</t>
+  </si>
+  <si>
+    <t>Feb 2026</t>
+  </si>
+  <si>
+    <t>Mar 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="14">
+  <numFmts count="15">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
@@ -3392,6 +3383,7 @@
     <numFmt numFmtId="174" formatCode="0.0&quot; months&quot;"/>
     <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0.00;\(&quot;$&quot;#,##0.00\);&quot;-&quot;"/>
+    <numFmt numFmtId="177" formatCode="mmm_yyyyy"/>
   </numFmts>
   <fonts count="48" x14ac:knownFonts="1">
     <font>
@@ -3867,7 +3859,7 @@
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4052,15 +4044,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4075,10 +4058,7 @@
     </xf>
     <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4093,18 +4073,12 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4132,9 +4106,6 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="17" fontId="25" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="24" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="17" fontId="24" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -4143,26 +4114,28 @@
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="175" fontId="24" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="17" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="175" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="26">
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <name val="Calibri"/>
-      </font>
-      <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFB8CCE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="33">
     <dxf>
       <font>
         <b val="0"/>
@@ -4177,6 +4150,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0.00"/>
@@ -4201,6 +4175,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0.00"/>
@@ -4225,6 +4200,32 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFB8CCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -4248,6 +4249,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="22" formatCode="mmm/yy"/>
@@ -4542,6 +4544,100 @@
     <dxf>
       <numFmt numFmtId="22" formatCode="mmm/yy"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEBF3FB"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEBF3FB"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEBF3FB"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEBF3FB"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEBF3FB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEBF3FB"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="22" formatCode="mmm/yy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFD9E1F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4556,14 +4652,26 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Michael Bezrukov" id="{E0CF43CD-786C-485F-8F02-5CFDECC1ADF9}" userId="c369a87971b237bd" providerId="Windows Live"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0792567E-A03E-4943-98E4-EB876B9B20D6}" name="WaterfallData" displayName="WaterfallData" ref="A1:E9" totalsRowCount="1">
-  <autoFilter ref="A1:E8" xr:uid="{0792567E-A03E-4943-98E4-EB876B9B20D6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33C032D8-7D31-427B-B687-D6ED9274A891}" name="KPI_Tracker" displayName="KPI_Tracker" ref="A3:E16" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+  <autoFilter ref="A3:E16" xr:uid="{33C032D8-7D31-427B-B687-D6ED9274A891}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{C557A6FD-F6C3-489A-869B-8E7220ED2F0F}" name="Metric" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{C8637273-2623-450B-8EC2-77599710AE46}" name="Jan 2026" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{36B839F2-DBCF-48CC-AD60-ACF3D6D67A87}" name="Feb 2026" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{CF28127B-1023-4FAA-8F51-4A1CC9FF9128}" name="Mar 2026" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{7BB998DD-A48B-4270-BB7C-2C1D3FA186B2}" name="Q1 2026" dataDxfId="26"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0792567E-A03E-4943-98E4-EB876B9B20D6}" name="WaterfallData" displayName="WaterfallData" ref="A1:E15" totalsRowCount="1">
+  <autoFilter ref="A1:E14" xr:uid="{0792567E-A03E-4943-98E4-EB876B9B20D6}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{E535E1E4-A65E-480E-B37A-792FC0723850}" name="Month" totalsRowFunction="custom" dataDxfId="25" totalsRowDxfId="4">
       <totalsRowFormula>TEXT(DATE(2026,2,1),"mmm-yy")</totalsRowFormula>
@@ -4576,14 +4684,14 @@
       <totalsRowFormula>'Feb 2026 A vs F'!C3</totalsRowFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{4D5B15AB-1D25-4871-B2A0-95F16E574BA9}" name="Variance" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="0">
-      <totalsRowFormula>C9-D9</totalsRowFormula>
+      <totalsRowFormula>C15-D15</totalsRowFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B284FA47-45D2-4122-AEB2-38E9A4BEAA57}" name="Table1" displayName="Table1" ref="A1:S98" totalsRowShown="0">
   <autoFilter ref="A1:S98" xr:uid="{4D0CD488-A2A9-4594-92D1-28BF2D26397C}"/>
   <tableColumns count="19">
@@ -4615,7 +4723,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{539C435F-C1A6-4146-89EF-73537E96D5A1}" name="SMSpend" displayName="SMSpend" ref="A66:J80" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="A66:J80" xr:uid="{B4D1F123-2972-489C-8FEC-9C6D26BDA440}"/>
   <tableColumns count="10">
@@ -4634,7 +4742,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B88C251F-7B17-4393-8014-7AFD83428EA2}" name="Table3" displayName="Table3" ref="A1:D7" totalsRowShown="0">
   <autoFilter ref="A1:D7" xr:uid="{D57C8F59-9D05-4E48-BB7C-E78657E107B1}"/>
   <tableColumns count="4">
@@ -4930,14 +5038,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D5" dT="2026-04-06T20:13:16.37" personId="{E0CF43CD-786C-485F-8F02-5CFDECC1ADF9}" id="{DABA5F44-B889-496F-A0C1-7D24F3B228AF}">
-    <text>The Jan 2026 A vs F file does not include Contraction MRR</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
   <wetp:taskpane dockstate="right" visibility="1" width="525" row="6">
@@ -6195,30 +6295,30 @@
       <c r="A47" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B47" s="124" t="s">
+      <c r="B47" s="177" t="s">
         <v>311</v>
       </c>
-      <c r="C47" s="124"/>
-      <c r="D47" s="124"/>
-      <c r="E47" s="124"/>
-      <c r="F47" s="124"/>
-      <c r="G47" s="124"/>
-      <c r="H47" s="124"/>
-      <c r="I47" s="124"/>
+      <c r="C47" s="177"/>
+      <c r="D47" s="177"/>
+      <c r="E47" s="177"/>
+      <c r="F47" s="177"/>
+      <c r="G47" s="177"/>
+      <c r="H47" s="177"/>
+      <c r="I47" s="177"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B49" s="124" t="s">
+      <c r="B49" s="177" t="s">
         <v>312</v>
       </c>
-      <c r="C49" s="124"/>
-      <c r="D49" s="124"/>
-      <c r="E49" s="124"/>
-      <c r="F49" s="124"/>
-      <c r="G49" s="124"/>
-      <c r="H49" s="124"/>
+      <c r="C49" s="177"/>
+      <c r="D49" s="177"/>
+      <c r="E49" s="177"/>
+      <c r="F49" s="177"/>
+      <c r="G49" s="177"/>
+      <c r="H49" s="177"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8587,35 +8687,35 @@
       </c>
     </row>
     <row r="34" spans="1:27" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="126" t="s">
+      <c r="A34" s="178" t="s">
         <v>188</v>
       </c>
-      <c r="B34" s="127"/>
-      <c r="C34" s="127"/>
-      <c r="D34" s="127"/>
-      <c r="E34" s="127"/>
-      <c r="F34" s="127"/>
-      <c r="G34" s="127"/>
-      <c r="H34" s="127"/>
-      <c r="I34" s="127"/>
-      <c r="J34" s="127"/>
-      <c r="K34" s="127"/>
-      <c r="L34" s="127"/>
-      <c r="M34" s="127"/>
-      <c r="N34" s="127"/>
-      <c r="O34" s="127"/>
-      <c r="P34" s="127"/>
-      <c r="Q34" s="127"/>
-      <c r="R34" s="127"/>
-      <c r="S34" s="127"/>
-      <c r="T34" s="127"/>
-      <c r="U34" s="127"/>
-      <c r="V34" s="127"/>
-      <c r="W34" s="127"/>
-      <c r="X34" s="127"/>
-      <c r="Y34" s="127"/>
-      <c r="Z34" s="127"/>
-      <c r="AA34" s="127"/>
+      <c r="B34" s="179"/>
+      <c r="C34" s="179"/>
+      <c r="D34" s="179"/>
+      <c r="E34" s="179"/>
+      <c r="F34" s="179"/>
+      <c r="G34" s="179"/>
+      <c r="H34" s="179"/>
+      <c r="I34" s="179"/>
+      <c r="J34" s="179"/>
+      <c r="K34" s="179"/>
+      <c r="L34" s="179"/>
+      <c r="M34" s="179"/>
+      <c r="N34" s="179"/>
+      <c r="O34" s="179"/>
+      <c r="P34" s="179"/>
+      <c r="Q34" s="179"/>
+      <c r="R34" s="179"/>
+      <c r="S34" s="179"/>
+      <c r="T34" s="179"/>
+      <c r="U34" s="179"/>
+      <c r="V34" s="179"/>
+      <c r="W34" s="179"/>
+      <c r="X34" s="179"/>
+      <c r="Y34" s="179"/>
+      <c r="Z34" s="179"/>
+      <c r="AA34" s="179"/>
     </row>
     <row r="35" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="1:27" x14ac:dyDescent="0.35">
@@ -8624,35 +8724,35 @@
       </c>
     </row>
     <row r="37" spans="1:27" ht="95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="126" t="s">
+      <c r="A37" s="178" t="s">
         <v>190</v>
       </c>
-      <c r="B37" s="127"/>
-      <c r="C37" s="127"/>
-      <c r="D37" s="127"/>
-      <c r="E37" s="127"/>
-      <c r="F37" s="127"/>
-      <c r="G37" s="127"/>
-      <c r="H37" s="127"/>
-      <c r="I37" s="127"/>
-      <c r="J37" s="127"/>
-      <c r="K37" s="127"/>
-      <c r="L37" s="127"/>
-      <c r="M37" s="127"/>
-      <c r="N37" s="127"/>
-      <c r="O37" s="127"/>
-      <c r="P37" s="127"/>
-      <c r="Q37" s="127"/>
-      <c r="R37" s="127"/>
-      <c r="S37" s="127"/>
-      <c r="T37" s="127"/>
-      <c r="U37" s="127"/>
-      <c r="V37" s="127"/>
-      <c r="W37" s="127"/>
-      <c r="X37" s="127"/>
-      <c r="Y37" s="127"/>
-      <c r="Z37" s="127"/>
-      <c r="AA37" s="127"/>
+      <c r="B37" s="179"/>
+      <c r="C37" s="179"/>
+      <c r="D37" s="179"/>
+      <c r="E37" s="179"/>
+      <c r="F37" s="179"/>
+      <c r="G37" s="179"/>
+      <c r="H37" s="179"/>
+      <c r="I37" s="179"/>
+      <c r="J37" s="179"/>
+      <c r="K37" s="179"/>
+      <c r="L37" s="179"/>
+      <c r="M37" s="179"/>
+      <c r="N37" s="179"/>
+      <c r="O37" s="179"/>
+      <c r="P37" s="179"/>
+      <c r="Q37" s="179"/>
+      <c r="R37" s="179"/>
+      <c r="S37" s="179"/>
+      <c r="T37" s="179"/>
+      <c r="U37" s="179"/>
+      <c r="V37" s="179"/>
+      <c r="W37" s="179"/>
+      <c r="X37" s="179"/>
+      <c r="Y37" s="179"/>
+      <c r="Z37" s="179"/>
+      <c r="AA37" s="179"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9376,18 +9476,18 @@
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A64" s="128" t="s">
+      <c r="A64" s="180" t="s">
         <v>256</v>
       </c>
-      <c r="B64" s="128"/>
-      <c r="C64" s="128"/>
-      <c r="D64" s="128"/>
-      <c r="E64" s="128"/>
-      <c r="F64" s="128"/>
-      <c r="G64" s="128"/>
-      <c r="H64" s="128"/>
-      <c r="I64" s="128"/>
-      <c r="J64" s="128"/>
+      <c r="B64" s="180"/>
+      <c r="C64" s="180"/>
+      <c r="D64" s="180"/>
+      <c r="E64" s="180"/>
+      <c r="F64" s="180"/>
+      <c r="G64" s="180"/>
+      <c r="H64" s="180"/>
+      <c r="I64" s="180"/>
+      <c r="J64" s="180"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="62" t="s">
@@ -10539,882 +10639,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:I54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="9" max="9" width="48" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="25">
-        <f>'Forecast Assumptions'!B6</f>
-        <v>143069.5</v>
-      </c>
-      <c r="C7" s="25">
-        <f>B12</f>
-        <v>154354.1525</v>
-      </c>
-      <c r="D7" s="25">
-        <f>C12</f>
-        <v>172782.38173749999</v>
-      </c>
-      <c r="E7" s="25">
-        <f>D12</f>
-        <v>200718.46982881249</v>
-      </c>
-      <c r="G7" s="25">
-        <f>B7</f>
-        <v>143069.5</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="25">
-        <f>'Forecast Assumptions'!B12*'Forecast Assumptions'!B13</f>
-        <v>12000</v>
-      </c>
-      <c r="C8" s="25">
-        <f>'Forecast Assumptions'!C12*'Forecast Assumptions'!C13</f>
-        <v>19200</v>
-      </c>
-      <c r="D8" s="25">
-        <f>'Forecast Assumptions'!D12*'Forecast Assumptions'!D13</f>
-        <v>28800</v>
-      </c>
-      <c r="E8" s="25">
-        <f>'Forecast Assumptions'!E12*'Forecast Assumptions'!E13</f>
-        <v>30600</v>
-      </c>
-      <c r="G8" s="25">
-        <f>B8+C8+D8+E8</f>
-        <v>90600</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="25">
-        <f>B7*'Forecast Assumptions'!B14</f>
-        <v>2146.0425</v>
-      </c>
-      <c r="C9" s="25">
-        <f>C7*'Forecast Assumptions'!C14</f>
-        <v>2315.3122874999999</v>
-      </c>
-      <c r="D9" s="25">
-        <f>D7*'Forecast Assumptions'!D14</f>
-        <v>2591.7357260624999</v>
-      </c>
-      <c r="E9" s="25">
-        <f>E7*'Forecast Assumptions'!E14</f>
-        <v>3010.7770474321874</v>
-      </c>
-      <c r="G9" s="25">
-        <f>B9+C9+D9+E9</f>
-        <v>10063.867560994688</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="25">
-        <f>B7*'Forecast Assumptions'!B15</f>
-        <v>2861.39</v>
-      </c>
-      <c r="C10" s="25">
-        <f>C7*'Forecast Assumptions'!C15</f>
-        <v>3087.0830500000002</v>
-      </c>
-      <c r="D10" s="25">
-        <f>D7*'Forecast Assumptions'!D15</f>
-        <v>3455.6476347499997</v>
-      </c>
-      <c r="E10" s="25">
-        <f>E7*'Forecast Assumptions'!E15</f>
-        <v>4014.36939657625</v>
-      </c>
-      <c r="G10" s="25">
-        <f>B10+C10+D10+E10</f>
-        <v>13418.49008132625</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="26">
-        <f>B8+B9-B10</f>
-        <v>11284.6525</v>
-      </c>
-      <c r="C11" s="26">
-        <f>C8+C9-C10</f>
-        <v>18428.2292375</v>
-      </c>
-      <c r="D11" s="26">
-        <f>D8+D9-D10</f>
-        <v>27936.0880913125</v>
-      </c>
-      <c r="E11" s="26">
-        <f>E8+E9-E10</f>
-        <v>29596.407650855937</v>
-      </c>
-      <c r="G11" s="26">
-        <f>G8+G9-G10</f>
-        <v>87245.377479668445</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="26">
-        <f>B7+B11</f>
-        <v>154354.1525</v>
-      </c>
-      <c r="C12" s="26">
-        <f>C7+C11</f>
-        <v>172782.38173749999</v>
-      </c>
-      <c r="D12" s="26">
-        <f>D7+D11</f>
-        <v>200718.46982881249</v>
-      </c>
-      <c r="E12" s="26">
-        <f>E7+E11</f>
-        <v>230314.87747966842</v>
-      </c>
-      <c r="G12" s="26">
-        <f>E12</f>
-        <v>230314.87747966842</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" s="22">
-        <f>B12*12</f>
-        <v>1852249.83</v>
-      </c>
-      <c r="C13" s="22">
-        <f>C12*12</f>
-        <v>2073388.58085</v>
-      </c>
-      <c r="D13" s="22">
-        <f>D12*12</f>
-        <v>2408621.6379457498</v>
-      </c>
-      <c r="E13" s="22">
-        <f>E12*12</f>
-        <v>2763778.5297560208</v>
-      </c>
-      <c r="G13" s="22">
-        <f>G12*12</f>
-        <v>2763778.5297560208</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="G14" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="G15" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="G16" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="27">
-        <f>B12*3</f>
-        <v>463062.45750000002</v>
-      </c>
-      <c r="C20" s="27">
-        <f>C12*3</f>
-        <v>518347.14521250001</v>
-      </c>
-      <c r="D20" s="27">
-        <f>D12*3</f>
-        <v>602155.40948643745</v>
-      </c>
-      <c r="E20" s="27">
-        <f>E12*3</f>
-        <v>690944.63243900519</v>
-      </c>
-      <c r="G20" s="27">
-        <f>B20+C20+D20+E20</f>
-        <v>2274509.6446379428</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B21" s="27">
-        <f>B20*(1-'Forecast Assumptions'!B22)</f>
-        <v>138918.73725000003</v>
-      </c>
-      <c r="C21" s="27">
-        <f>C20*(1-'Forecast Assumptions'!B22)</f>
-        <v>155504.14356375003</v>
-      </c>
-      <c r="D21" s="27">
-        <f>D20*(1-'Forecast Assumptions'!B22)</f>
-        <v>180646.62284593127</v>
-      </c>
-      <c r="E21" s="27">
-        <f>E20*(1-'Forecast Assumptions'!B22)</f>
-        <v>207283.38973170158</v>
-      </c>
-      <c r="G21" s="27">
-        <f>B21+C21+D21+E21</f>
-        <v>682352.89339138288</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="22">
-        <f>B20-B21</f>
-        <v>324143.72025000001</v>
-      </c>
-      <c r="C22" s="22">
-        <f>C20-C21</f>
-        <v>362843.00164874998</v>
-      </c>
-      <c r="D22" s="22">
-        <f>D20-D21</f>
-        <v>421508.78664050618</v>
-      </c>
-      <c r="E22" s="22">
-        <f>E20-E21</f>
-        <v>483661.24270730361</v>
-      </c>
-      <c r="G22" s="22">
-        <f>B22+C22+D22+E22</f>
-        <v>1592156.7512465599</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="28">
-        <f>B22/B20</f>
-        <v>0.7</v>
-      </c>
-      <c r="C23" s="28">
-        <f>C22/C20</f>
-        <v>0.7</v>
-      </c>
-      <c r="D23" s="28">
-        <f>D22/D20</f>
-        <v>0.7</v>
-      </c>
-      <c r="E23" s="28">
-        <f>E22/E20</f>
-        <v>0.7</v>
-      </c>
-      <c r="G23" s="28">
-        <f>G22/G20</f>
-        <v>0.7</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="7"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="27">
-        <f>'Forecast Assumptions'!B26</f>
-        <v>90000</v>
-      </c>
-      <c r="C25" s="27">
-        <f>'Forecast Assumptions'!C26</f>
-        <v>90000</v>
-      </c>
-      <c r="D25" s="27">
-        <f>'Forecast Assumptions'!D26</f>
-        <v>108000</v>
-      </c>
-      <c r="E25" s="27">
-        <f>'Forecast Assumptions'!E26</f>
-        <v>108000</v>
-      </c>
-      <c r="G25" s="27">
-        <f>B25+C25+D25+E25</f>
-        <v>396000</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B26" s="27">
-        <f>'Forecast Assumptions'!B27</f>
-        <v>75000</v>
-      </c>
-      <c r="C26" s="27">
-        <f>'Forecast Assumptions'!C27</f>
-        <v>75000</v>
-      </c>
-      <c r="D26" s="27">
-        <f>'Forecast Assumptions'!D27</f>
-        <v>75000</v>
-      </c>
-      <c r="E26" s="27">
-        <f>'Forecast Assumptions'!E27</f>
-        <v>75000</v>
-      </c>
-      <c r="G26" s="27">
-        <f>B26+C26+D26+E26</f>
-        <v>300000</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" s="27">
-        <f>'Forecast Assumptions'!B28</f>
-        <v>57000</v>
-      </c>
-      <c r="C27" s="27">
-        <f>'Forecast Assumptions'!C28</f>
-        <v>57000</v>
-      </c>
-      <c r="D27" s="27">
-        <f>'Forecast Assumptions'!D28</f>
-        <v>57000</v>
-      </c>
-      <c r="E27" s="27">
-        <f>'Forecast Assumptions'!E28</f>
-        <v>57000</v>
-      </c>
-      <c r="G27" s="27">
-        <f>B27+C27+D27+E27</f>
-        <v>228000</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="22">
-        <f>B25+B26+B27</f>
-        <v>222000</v>
-      </c>
-      <c r="C28" s="22">
-        <f>C25+C26+C27</f>
-        <v>222000</v>
-      </c>
-      <c r="D28" s="22">
-        <f>D25+D26+D27</f>
-        <v>240000</v>
-      </c>
-      <c r="E28" s="22">
-        <f>E25+E26+E27</f>
-        <v>240000</v>
-      </c>
-      <c r="G28" s="22">
-        <f>G25+G26+G27</f>
-        <v>924000</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="7"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="29">
-        <f>B22-B28</f>
-        <v>102143.72025000001</v>
-      </c>
-      <c r="C30" s="29">
-        <f>C22-C28</f>
-        <v>140843.00164874998</v>
-      </c>
-      <c r="D30" s="29">
-        <f>D22-D28</f>
-        <v>181508.78664050618</v>
-      </c>
-      <c r="E30" s="29">
-        <f>E22-E28</f>
-        <v>243661.24270730361</v>
-      </c>
-      <c r="G30" s="29">
-        <f>B30+C30+D30+E30</f>
-        <v>668156.75124655978</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="28">
-        <f>B30/B20</f>
-        <v>0.22058303063793508</v>
-      </c>
-      <c r="C31" s="28">
-        <f>C30/C20</f>
-        <v>0.27171559243566473</v>
-      </c>
-      <c r="D31" s="28">
-        <f>D30/D20</f>
-        <v>0.30143179614596549</v>
-      </c>
-      <c r="E31" s="28">
-        <f>E30/E20</f>
-        <v>0.3526494472461415</v>
-      </c>
-      <c r="G31" s="28">
-        <f>G30/G20</f>
-        <v>0.29375859224062212</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B34" s="30">
-        <f>E12</f>
-        <v>230314.87747966842</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A35" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B35" s="27">
-        <f>B34*12</f>
-        <v>2763778.5297560208</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B36" s="27">
-        <f>G20</f>
-        <v>2274509.6446379428</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A37" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B37" s="28">
-        <f>(E12-B7)/B7</f>
-        <v>0.60981115807120612</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A38" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B38" s="31">
-        <f>'Forecast Assumptions'!B12+'Forecast Assumptions'!C12+'Forecast Assumptions'!D12+'Forecast Assumptions'!E12</f>
-        <v>28</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A39" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B39" s="27">
-        <f>G25/B38</f>
-        <v>14142.857142857143</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A40" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B40" s="28">
-        <f>(E12/B7)^(1/12)-1</f>
-        <v>4.0474029164477399E-2</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A43" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="B43" s="33"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="94" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A44" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="B44" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="C44" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="D44" s="34" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A45" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B45" s="25">
-        <v>154354.15</v>
-      </c>
-      <c r="C45" s="13">
-        <f>B12</f>
-        <v>154354.1525</v>
-      </c>
-      <c r="D45" s="14" t="str">
-        <f t="shared" ref="D45:D50" si="0">IF(ROUND(C45,2)=ROUND(B45,2),"✓","✗ diff: "&amp;TEXT(C45-B45,"$#,##0.00"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A46" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B46" s="25">
-        <v>172782.38</v>
-      </c>
-      <c r="C46" s="13">
-        <f>C12</f>
-        <v>172782.38173749999</v>
-      </c>
-      <c r="D46" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A47" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B47" s="25">
-        <v>200718.47</v>
-      </c>
-      <c r="C47" s="13">
-        <f>D12</f>
-        <v>200718.46982881249</v>
-      </c>
-      <c r="D47" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A48" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B48" s="25">
-        <v>230314.88</v>
-      </c>
-      <c r="C48" s="13">
-        <f>E12</f>
-        <v>230314.87747966842</v>
-      </c>
-      <c r="D48" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B49" s="25">
-        <v>2274509.64</v>
-      </c>
-      <c r="C49" s="13">
-        <f>G20</f>
-        <v>2274509.6446379428</v>
-      </c>
-      <c r="D49" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B50" s="25">
-        <v>668156.75</v>
-      </c>
-      <c r="C50" s="13">
-        <f>G30</f>
-        <v>668156.75124655978</v>
-      </c>
-      <c r="D50" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B51" s="35">
-        <v>0.29399999999999998</v>
-      </c>
-      <c r="C51" s="12">
-        <f>G31</f>
-        <v>0.29375859224062212</v>
-      </c>
-      <c r="D51" s="14" t="str">
-        <f>IF(ROUND(C51,3)=ROUND(B51,3),"✓","✗ diff: "&amp;TEXT(C51-B51,"0.0%"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B52" s="36">
-        <v>28</v>
-      </c>
-      <c r="C52" s="11">
-        <f>B38</f>
-        <v>28</v>
-      </c>
-      <c r="D52" s="14" t="str">
-        <f>IF(C52=B52,"✓","✗ diff: "&amp;(C52-B52))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B53" s="25">
-        <v>14142.86</v>
-      </c>
-      <c r="C53" s="13">
-        <f>B39</f>
-        <v>14142.857142857143</v>
-      </c>
-      <c r="D53" s="14" t="str">
-        <f>IF(ROUND(C53,2)=ROUND(B53,2),"✓","✗ diff: "&amp;TEXT(C53-B53,"$#,##0.00"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B54" s="35">
-        <v>0.04</v>
-      </c>
-      <c r="C54" s="12">
-        <f>B40</f>
-        <v>4.0474029164477399E-2</v>
-      </c>
-      <c r="D54" s="14" t="str">
-        <f>IF(ROUND(C54,2)=ROUND(B54,2),"✓","✗ diff: "&amp;TEXT(C54-B54,"0.00%"))</f>
-        <v>✓</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC3BD98E-4DD3-4CB1-9EF7-22E4D369D9B8}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -12236,6 +11460,882 @@
   <ignoredErrors>
     <ignoredError sqref="F7 F15" formula="1"/>
   </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:I54"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="9" max="9" width="48" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="25">
+        <f>'Forecast Assumptions'!B6</f>
+        <v>143069.5</v>
+      </c>
+      <c r="C7" s="25">
+        <f>B12</f>
+        <v>154354.1525</v>
+      </c>
+      <c r="D7" s="25">
+        <f>C12</f>
+        <v>172782.38173749999</v>
+      </c>
+      <c r="E7" s="25">
+        <f>D12</f>
+        <v>200718.46982881249</v>
+      </c>
+      <c r="G7" s="25">
+        <f>B7</f>
+        <v>143069.5</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="25">
+        <f>'Forecast Assumptions'!B12*'Forecast Assumptions'!B13</f>
+        <v>12000</v>
+      </c>
+      <c r="C8" s="25">
+        <f>'Forecast Assumptions'!C12*'Forecast Assumptions'!C13</f>
+        <v>19200</v>
+      </c>
+      <c r="D8" s="25">
+        <f>'Forecast Assumptions'!D12*'Forecast Assumptions'!D13</f>
+        <v>28800</v>
+      </c>
+      <c r="E8" s="25">
+        <f>'Forecast Assumptions'!E12*'Forecast Assumptions'!E13</f>
+        <v>30600</v>
+      </c>
+      <c r="G8" s="25">
+        <f>B8+C8+D8+E8</f>
+        <v>90600</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="25">
+        <f>B7*'Forecast Assumptions'!B14</f>
+        <v>2146.0425</v>
+      </c>
+      <c r="C9" s="25">
+        <f>C7*'Forecast Assumptions'!C14</f>
+        <v>2315.3122874999999</v>
+      </c>
+      <c r="D9" s="25">
+        <f>D7*'Forecast Assumptions'!D14</f>
+        <v>2591.7357260624999</v>
+      </c>
+      <c r="E9" s="25">
+        <f>E7*'Forecast Assumptions'!E14</f>
+        <v>3010.7770474321874</v>
+      </c>
+      <c r="G9" s="25">
+        <f>B9+C9+D9+E9</f>
+        <v>10063.867560994688</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="25">
+        <f>B7*'Forecast Assumptions'!B15</f>
+        <v>2861.39</v>
+      </c>
+      <c r="C10" s="25">
+        <f>C7*'Forecast Assumptions'!C15</f>
+        <v>3087.0830500000002</v>
+      </c>
+      <c r="D10" s="25">
+        <f>D7*'Forecast Assumptions'!D15</f>
+        <v>3455.6476347499997</v>
+      </c>
+      <c r="E10" s="25">
+        <f>E7*'Forecast Assumptions'!E15</f>
+        <v>4014.36939657625</v>
+      </c>
+      <c r="G10" s="25">
+        <f>B10+C10+D10+E10</f>
+        <v>13418.49008132625</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="26">
+        <f>B8+B9-B10</f>
+        <v>11284.6525</v>
+      </c>
+      <c r="C11" s="26">
+        <f>C8+C9-C10</f>
+        <v>18428.2292375</v>
+      </c>
+      <c r="D11" s="26">
+        <f>D8+D9-D10</f>
+        <v>27936.0880913125</v>
+      </c>
+      <c r="E11" s="26">
+        <f>E8+E9-E10</f>
+        <v>29596.407650855937</v>
+      </c>
+      <c r="G11" s="26">
+        <f>G8+G9-G10</f>
+        <v>87245.377479668445</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="26">
+        <f>B7+B11</f>
+        <v>154354.1525</v>
+      </c>
+      <c r="C12" s="26">
+        <f>C7+C11</f>
+        <v>172782.38173749999</v>
+      </c>
+      <c r="D12" s="26">
+        <f>D7+D11</f>
+        <v>200718.46982881249</v>
+      </c>
+      <c r="E12" s="26">
+        <f>E7+E11</f>
+        <v>230314.87747966842</v>
+      </c>
+      <c r="G12" s="26">
+        <f>E12</f>
+        <v>230314.87747966842</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="22">
+        <f>B12*12</f>
+        <v>1852249.83</v>
+      </c>
+      <c r="C13" s="22">
+        <f>C12*12</f>
+        <v>2073388.58085</v>
+      </c>
+      <c r="D13" s="22">
+        <f>D12*12</f>
+        <v>2408621.6379457498</v>
+      </c>
+      <c r="E13" s="22">
+        <f>E12*12</f>
+        <v>2763778.5297560208</v>
+      </c>
+      <c r="G13" s="22">
+        <f>G12*12</f>
+        <v>2763778.5297560208</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G14" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G15" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G16" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="27">
+        <f>B12*3</f>
+        <v>463062.45750000002</v>
+      </c>
+      <c r="C20" s="27">
+        <f>C12*3</f>
+        <v>518347.14521250001</v>
+      </c>
+      <c r="D20" s="27">
+        <f>D12*3</f>
+        <v>602155.40948643745</v>
+      </c>
+      <c r="E20" s="27">
+        <f>E12*3</f>
+        <v>690944.63243900519</v>
+      </c>
+      <c r="G20" s="27">
+        <f>B20+C20+D20+E20</f>
+        <v>2274509.6446379428</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="27">
+        <f>B20*(1-'Forecast Assumptions'!B22)</f>
+        <v>138918.73725000003</v>
+      </c>
+      <c r="C21" s="27">
+        <f>C20*(1-'Forecast Assumptions'!B22)</f>
+        <v>155504.14356375003</v>
+      </c>
+      <c r="D21" s="27">
+        <f>D20*(1-'Forecast Assumptions'!B22)</f>
+        <v>180646.62284593127</v>
+      </c>
+      <c r="E21" s="27">
+        <f>E20*(1-'Forecast Assumptions'!B22)</f>
+        <v>207283.38973170158</v>
+      </c>
+      <c r="G21" s="27">
+        <f>B21+C21+D21+E21</f>
+        <v>682352.89339138288</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="22">
+        <f>B20-B21</f>
+        <v>324143.72025000001</v>
+      </c>
+      <c r="C22" s="22">
+        <f>C20-C21</f>
+        <v>362843.00164874998</v>
+      </c>
+      <c r="D22" s="22">
+        <f>D20-D21</f>
+        <v>421508.78664050618</v>
+      </c>
+      <c r="E22" s="22">
+        <f>E20-E21</f>
+        <v>483661.24270730361</v>
+      </c>
+      <c r="G22" s="22">
+        <f>B22+C22+D22+E22</f>
+        <v>1592156.7512465599</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="28">
+        <f>B22/B20</f>
+        <v>0.7</v>
+      </c>
+      <c r="C23" s="28">
+        <f>C22/C20</f>
+        <v>0.7</v>
+      </c>
+      <c r="D23" s="28">
+        <f>D22/D20</f>
+        <v>0.7</v>
+      </c>
+      <c r="E23" s="28">
+        <f>E22/E20</f>
+        <v>0.7</v>
+      </c>
+      <c r="G23" s="28">
+        <f>G22/G20</f>
+        <v>0.7</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="7"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="27">
+        <f>'Forecast Assumptions'!B26</f>
+        <v>90000</v>
+      </c>
+      <c r="C25" s="27">
+        <f>'Forecast Assumptions'!C26</f>
+        <v>90000</v>
+      </c>
+      <c r="D25" s="27">
+        <f>'Forecast Assumptions'!D26</f>
+        <v>108000</v>
+      </c>
+      <c r="E25" s="27">
+        <f>'Forecast Assumptions'!E26</f>
+        <v>108000</v>
+      </c>
+      <c r="G25" s="27">
+        <f>B25+C25+D25+E25</f>
+        <v>396000</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="27">
+        <f>'Forecast Assumptions'!B27</f>
+        <v>75000</v>
+      </c>
+      <c r="C26" s="27">
+        <f>'Forecast Assumptions'!C27</f>
+        <v>75000</v>
+      </c>
+      <c r="D26" s="27">
+        <f>'Forecast Assumptions'!D27</f>
+        <v>75000</v>
+      </c>
+      <c r="E26" s="27">
+        <f>'Forecast Assumptions'!E27</f>
+        <v>75000</v>
+      </c>
+      <c r="G26" s="27">
+        <f>B26+C26+D26+E26</f>
+        <v>300000</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="27">
+        <f>'Forecast Assumptions'!B28</f>
+        <v>57000</v>
+      </c>
+      <c r="C27" s="27">
+        <f>'Forecast Assumptions'!C28</f>
+        <v>57000</v>
+      </c>
+      <c r="D27" s="27">
+        <f>'Forecast Assumptions'!D28</f>
+        <v>57000</v>
+      </c>
+      <c r="E27" s="27">
+        <f>'Forecast Assumptions'!E28</f>
+        <v>57000</v>
+      </c>
+      <c r="G27" s="27">
+        <f>B27+C27+D27+E27</f>
+        <v>228000</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="22">
+        <f>B25+B26+B27</f>
+        <v>222000</v>
+      </c>
+      <c r="C28" s="22">
+        <f>C25+C26+C27</f>
+        <v>222000</v>
+      </c>
+      <c r="D28" s="22">
+        <f>D25+D26+D27</f>
+        <v>240000</v>
+      </c>
+      <c r="E28" s="22">
+        <f>E25+E26+E27</f>
+        <v>240000</v>
+      </c>
+      <c r="G28" s="22">
+        <f>G25+G26+G27</f>
+        <v>924000</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="7"/>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="29">
+        <f>B22-B28</f>
+        <v>102143.72025000001</v>
+      </c>
+      <c r="C30" s="29">
+        <f>C22-C28</f>
+        <v>140843.00164874998</v>
+      </c>
+      <c r="D30" s="29">
+        <f>D22-D28</f>
+        <v>181508.78664050618</v>
+      </c>
+      <c r="E30" s="29">
+        <f>E22-E28</f>
+        <v>243661.24270730361</v>
+      </c>
+      <c r="G30" s="29">
+        <f>B30+C30+D30+E30</f>
+        <v>668156.75124655978</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="28">
+        <f>B30/B20</f>
+        <v>0.22058303063793508</v>
+      </c>
+      <c r="C31" s="28">
+        <f>C30/C20</f>
+        <v>0.27171559243566473</v>
+      </c>
+      <c r="D31" s="28">
+        <f>D30/D20</f>
+        <v>0.30143179614596549</v>
+      </c>
+      <c r="E31" s="28">
+        <f>E30/E20</f>
+        <v>0.3526494472461415</v>
+      </c>
+      <c r="G31" s="28">
+        <f>G30/G20</f>
+        <v>0.29375859224062212</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="30">
+        <f>E12</f>
+        <v>230314.87747966842</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="27">
+        <f>B34*12</f>
+        <v>2763778.5297560208</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" s="27">
+        <f>G20</f>
+        <v>2274509.6446379428</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B37" s="28">
+        <f>(E12-B7)/B7</f>
+        <v>0.60981115807120612</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B38" s="31">
+        <f>'Forecast Assumptions'!B12+'Forecast Assumptions'!C12+'Forecast Assumptions'!D12+'Forecast Assumptions'!E12</f>
+        <v>28</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B39" s="27">
+        <f>G25/B38</f>
+        <v>14142.857142857143</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B40" s="28">
+        <f>(E12/B7)^(1/12)-1</f>
+        <v>4.0474029164477399E-2</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" s="33"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="94" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="34" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" s="25">
+        <v>154354.15</v>
+      </c>
+      <c r="C45" s="13">
+        <f>B12</f>
+        <v>154354.1525</v>
+      </c>
+      <c r="D45" s="14" t="str">
+        <f t="shared" ref="D45:D50" si="0">IF(ROUND(C45,2)=ROUND(B45,2),"✓","✗ diff: "&amp;TEXT(C45-B45,"$#,##0.00"))</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" s="25">
+        <v>172782.38</v>
+      </c>
+      <c r="C46" s="13">
+        <f>C12</f>
+        <v>172782.38173749999</v>
+      </c>
+      <c r="D46" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" s="25">
+        <v>200718.47</v>
+      </c>
+      <c r="C47" s="13">
+        <f>D12</f>
+        <v>200718.46982881249</v>
+      </c>
+      <c r="D47" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" s="25">
+        <v>230314.88</v>
+      </c>
+      <c r="C48" s="13">
+        <f>E12</f>
+        <v>230314.87747966842</v>
+      </c>
+      <c r="D48" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="25">
+        <v>2274509.64</v>
+      </c>
+      <c r="C49" s="13">
+        <f>G20</f>
+        <v>2274509.6446379428</v>
+      </c>
+      <c r="D49" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="25">
+        <v>668156.75</v>
+      </c>
+      <c r="C50" s="13">
+        <f>G30</f>
+        <v>668156.75124655978</v>
+      </c>
+      <c r="D50" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="35">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="C51" s="12">
+        <f>G31</f>
+        <v>0.29375859224062212</v>
+      </c>
+      <c r="D51" s="14" t="str">
+        <f>IF(ROUND(C51,3)=ROUND(B51,3),"✓","✗ diff: "&amp;TEXT(C51-B51,"0.0%"))</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" s="36">
+        <v>28</v>
+      </c>
+      <c r="C52" s="11">
+        <f>B38</f>
+        <v>28</v>
+      </c>
+      <c r="D52" s="14" t="str">
+        <f>IF(C52=B52,"✓","✗ diff: "&amp;(C52-B52))</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B53" s="25">
+        <v>14142.86</v>
+      </c>
+      <c r="C53" s="13">
+        <f>B39</f>
+        <v>14142.857142857143</v>
+      </c>
+      <c r="D53" s="14" t="str">
+        <f>IF(ROUND(C53,2)=ROUND(B53,2),"✓","✗ diff: "&amp;TEXT(C53-B53,"$#,##0.00"))</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B54" s="35">
+        <v>0.04</v>
+      </c>
+      <c r="C54" s="12">
+        <f>B40</f>
+        <v>4.0474029164477399E-2</v>
+      </c>
+      <c r="D54" s="14" t="str">
+        <f>IF(ROUND(C54,2)=ROUND(B54,2),"✓","✗ diff: "&amp;TEXT(C54-B54,"0.00%"))</f>
+        <v>✓</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -12256,278 +12356,278 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="125" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="131" t="s">
+      <c r="B2" s="126" t="s">
         <v>656</v>
       </c>
-      <c r="C2" s="131" t="s">
+      <c r="C2" s="126" t="s">
         <v>657</v>
       </c>
-      <c r="D2" s="131" t="s">
+      <c r="D2" s="126" t="s">
         <v>597</v>
       </c>
-      <c r="E2" s="131" t="s">
+      <c r="E2" s="126" t="s">
         <v>598</v>
       </c>
-      <c r="F2" s="131" t="s">
+      <c r="F2" s="126" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="132" t="s">
+      <c r="A3" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="134">
+      <c r="B3" s="129">
         <f>'Jan 2026 A vs F '!B9</f>
         <v>144779.5</v>
       </c>
-      <c r="C3" s="134">
+      <c r="C3" s="129">
         <f>'Jan 2026 A vs F '!B9</f>
         <v>144779.5</v>
       </c>
-      <c r="D3" s="134">
-        <f>B3-C3</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="135">
+      <c r="D3" s="129">
+        <f t="shared" ref="D3:D10" si="0">B3-C3</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="130">
         <f>IFERROR(B3/C3-1, 0)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="136" t="str" cm="1">
+      <c r="F3" s="131" t="str" cm="1">
         <f t="array" ref="F3">_xlfn.IFS(D3&lt;0, "U", D3&gt;0, "F", D3=0, "-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="171" t="s">
+      <c r="A4" s="159" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="134">
+      <c r="B4" s="129">
         <v>6120</v>
       </c>
-      <c r="C4" s="134">
+      <c r="C4" s="129">
         <v>4000</v>
       </c>
-      <c r="D4" s="134">
-        <f>B4-C4</f>
+      <c r="D4" s="129">
+        <f t="shared" si="0"/>
         <v>2120</v>
       </c>
-      <c r="E4" s="135">
+      <c r="E4" s="130">
         <f>IFERROR(B4/C4-1, 0)</f>
         <v>0.53</v>
       </c>
-      <c r="F4" s="136" t="str" cm="1">
+      <c r="F4" s="131" t="str" cm="1">
         <f t="array" ref="F4">_xlfn.IFS(D4&lt;0, "U", D4&gt;0, "F", D4=0, "-")</f>
         <v>F</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="171" t="s">
+      <c r="A5" s="159" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="134">
-        <v>0</v>
-      </c>
-      <c r="C5" s="134">
+      <c r="B5" s="129">
+        <v>0</v>
+      </c>
+      <c r="C5" s="129">
         <f>'2026 Forecast'!B9/3</f>
         <v>715.34749999999997</v>
       </c>
-      <c r="D5" s="134">
-        <f>B5-C5</f>
+      <c r="D5" s="129">
+        <f t="shared" si="0"/>
         <v>-715.34749999999997</v>
       </c>
-      <c r="E5" s="135">
+      <c r="E5" s="130">
         <f>IFERROR(B5/C5-1, 0)</f>
         <v>-1</v>
       </c>
-      <c r="F5" s="136" t="str" cm="1">
+      <c r="F5" s="131" t="str" cm="1">
         <f t="array" ref="F5">_xlfn.IFS(D5&lt;0, "U", D5&gt;0, "F", D5=0, "-")</f>
         <v>U</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="132" t="s">
+      <c r="A6" s="127" t="s">
         <v>655</v>
       </c>
-      <c r="B6" s="134">
-        <v>0</v>
-      </c>
-      <c r="C6" s="134">
-        <v>0</v>
-      </c>
-      <c r="D6" s="134">
-        <f>B6-C6</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="135">
+      <c r="B6" s="129">
+        <v>0</v>
+      </c>
+      <c r="C6" s="129">
+        <v>0</v>
+      </c>
+      <c r="D6" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="130">
         <f>IFERROR(B6/C6-1, 0)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="136" t="str" cm="1">
+      <c r="F6" s="131" t="str" cm="1">
         <f t="array" ref="F6">_xlfn.IFS(D6&lt;0, "U", D6&gt;0, "F", D6=0, "-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="139" t="s">
+      <c r="A7" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="140">
+      <c r="B7" s="129">
         <v>594</v>
       </c>
-      <c r="C7" s="140">
+      <c r="C7" s="129">
         <f>'2026 Forecast'!B10/3</f>
         <v>953.79666666666662</v>
       </c>
-      <c r="D7" s="140">
-        <f>B7-C7</f>
+      <c r="D7" s="129">
+        <f t="shared" si="0"/>
         <v>-359.79666666666662</v>
       </c>
-      <c r="E7" s="141">
+      <c r="E7" s="130">
         <f>IFERROR(B7/C7-1, 0)</f>
         <v>-0.37722575391680269</v>
       </c>
-      <c r="F7" s="142" t="str" cm="1">
+      <c r="F7" s="134" t="str" cm="1">
         <f t="array" ref="F7">_xlfn.IFS(D7&gt;0, "U", D7&lt;0, "F", D7=0, "-")</f>
         <v>F</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="143" t="s">
+      <c r="A8" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="144">
+      <c r="B8" s="136">
         <f>B4+B5-B7</f>
         <v>5526</v>
       </c>
-      <c r="C8" s="144">
+      <c r="C8" s="136">
         <f>C4+C5-C7</f>
         <v>3761.5508333333332</v>
       </c>
-      <c r="D8" s="144">
-        <f>B8-C8</f>
+      <c r="D8" s="136">
+        <f t="shared" si="0"/>
         <v>1764.4491666666668</v>
       </c>
-      <c r="E8" s="145">
+      <c r="E8" s="137">
         <f>B8/C8-1</f>
         <v>0.46907492277675367</v>
       </c>
-      <c r="F8" s="146" t="str" cm="1">
+      <c r="F8" s="138" t="str" cm="1">
         <f t="array" ref="F8">_xlfn.IFS(D8&lt;0, "U", D8&gt;0, "F", D8=0, "-")</f>
         <v>F</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="147" t="s">
+      <c r="A9" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="148">
+      <c r="B9" s="140">
         <f>B3+B4+B5-B7</f>
         <v>150305.5</v>
       </c>
-      <c r="C9" s="148">
+      <c r="C9" s="140">
         <f>C3+C8</f>
         <v>148541.05083333334</v>
       </c>
-      <c r="D9" s="148">
-        <f>B9-C9</f>
+      <c r="D9" s="140">
+        <f t="shared" si="0"/>
         <v>1764.4491666666581</v>
       </c>
-      <c r="E9" s="149">
+      <c r="E9" s="141">
         <f>B9/C9-1</f>
         <v>1.1878528910142183E-2</v>
       </c>
-      <c r="F9" s="150" t="str" cm="1">
+      <c r="F9" s="142" t="str" cm="1">
         <f t="array" ref="F9">_xlfn.IFS(D9&lt;0, "U", D9&gt;0, "F", D9=0, "-")</f>
         <v>F</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="151" t="s">
+      <c r="A10" s="128" t="s">
         <v>112</v>
       </c>
-      <c r="B10" s="152">
+      <c r="B10" s="143">
         <f>B9*12</f>
         <v>1803666</v>
       </c>
-      <c r="C10" s="152">
+      <c r="C10" s="143">
         <f>C9*12</f>
         <v>1782492.61</v>
       </c>
-      <c r="D10" s="152">
-        <f>B10-C10</f>
+      <c r="D10" s="143">
+        <f t="shared" si="0"/>
         <v>21173.389999999898</v>
       </c>
-      <c r="E10" s="153">
+      <c r="E10" s="144">
         <f>B10/C10-1</f>
         <v>1.1878528910142183E-2</v>
       </c>
-      <c r="F10" s="154" t="str" cm="1">
+      <c r="F10" s="145" t="str" cm="1">
         <f t="array" ref="F10">_xlfn.IFS(D10&lt;0, "U", D10&gt;0, "F", D10=0, "-")</f>
         <v>F</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="155"/>
-      <c r="B11" s="155"/>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155"/>
-      <c r="E11" s="155"/>
-      <c r="F11" s="155"/>
+      <c r="A11" s="146"/>
+      <c r="B11" s="146"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="146"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="133" t="s">
+      <c r="A12" s="128" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="131" t="s">
+      <c r="A13" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="131" t="s">
+      <c r="B13" s="126" t="s">
         <v>656</v>
       </c>
-      <c r="C13" s="131" t="s">
+      <c r="C13" s="126" t="s">
         <v>657</v>
       </c>
-      <c r="D13" s="131" t="s">
+      <c r="D13" s="126" t="s">
         <v>597</v>
       </c>
-      <c r="E13" s="131" t="s">
+      <c r="E13" s="126" t="s">
         <v>598</v>
       </c>
-      <c r="F13" s="131" t="s">
+      <c r="F13" s="126" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="133" t="s">
+      <c r="A14" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="137">
+      <c r="B14" s="132">
         <f>B9</f>
         <v>150305.5</v>
       </c>
-      <c r="C14" s="137">
+      <c r="C14" s="132">
         <f>C9</f>
         <v>148541.05083333334</v>
       </c>
-      <c r="D14" s="137">
-        <f>B14-C14</f>
+      <c r="D14" s="132">
+        <f t="shared" ref="D14:D23" si="1">B14-C14</f>
         <v>1764.4491666666581</v>
       </c>
-      <c r="E14" s="138">
-        <f>B14/C14-1</f>
+      <c r="E14" s="133">
+        <f t="shared" ref="E14:E23" si="2">B14/C14-1</f>
         <v>1.1878528910142183E-2</v>
       </c>
-      <c r="F14" s="136" t="str" cm="1">
+      <c r="F14" s="131" t="str" cm="1">
         <f t="array" ref="F14">_xlfn.IFS(D14&lt;0, "U", D14&gt;0, "F", D14=0, "-")</f>
         <v>F</v>
       </c>
@@ -12536,26 +12636,26 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="151" t="s">
+      <c r="A15" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="156">
+      <c r="B15" s="132">
         <f>B14*(1-B17)</f>
         <v>45091.650000000009</v>
       </c>
-      <c r="C15" s="156">
+      <c r="C15" s="132">
         <f>C14*0.3</f>
         <v>44562.31525</v>
       </c>
-      <c r="D15" s="156">
-        <f>B15-C15</f>
+      <c r="D15" s="132">
+        <f t="shared" si="1"/>
         <v>529.33475000000908</v>
       </c>
-      <c r="E15" s="157">
-        <f>B15/C15-1</f>
+      <c r="E15" s="133">
+        <f t="shared" si="2"/>
         <v>1.1878528910142405E-2</v>
       </c>
-      <c r="F15" s="158" t="str" cm="1">
+      <c r="F15" s="131" t="str" cm="1">
         <f t="array" ref="F15">_xlfn.IFS(D15&gt;0, "U", D15&lt;0, "F", D15=0, "-")</f>
         <v>U</v>
       </c>
@@ -12564,26 +12664,26 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="143" t="s">
+      <c r="A16" s="135" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="159">
+      <c r="B16" s="147">
         <f>B14-B15</f>
         <v>105213.84999999999</v>
       </c>
-      <c r="C16" s="159">
+      <c r="C16" s="147">
         <f>C14-C15</f>
         <v>103978.73558333334</v>
       </c>
-      <c r="D16" s="159">
-        <f>B16-C16</f>
+      <c r="D16" s="147">
+        <f t="shared" si="1"/>
         <v>1235.114416666649</v>
       </c>
-      <c r="E16" s="160">
-        <f>B16/C16-1</f>
+      <c r="E16" s="148">
+        <f t="shared" si="2"/>
         <v>1.1878528910142183E-2</v>
       </c>
-      <c r="F16" s="161" t="str" cm="1">
+      <c r="F16" s="149" t="str" cm="1">
         <f t="array" ref="F16">_xlfn.IFS(D16&lt;0, "U", D16&gt;0, "F", D16=0, "-")</f>
         <v>F</v>
       </c>
@@ -12592,25 +12692,25 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="147" t="s">
+      <c r="A17" s="139" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="169">
+      <c r="B17" s="157">
         <v>0.7</v>
       </c>
-      <c r="C17" s="168">
+      <c r="C17" s="156">
         <f>C16/C14</f>
         <v>0.70000000000000007</v>
       </c>
-      <c r="D17" s="168">
-        <f>B17-C17</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="168">
-        <f>B17/C17-1</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="163" t="str" cm="1">
+      <c r="D17" s="156">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="156">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="151" t="str" cm="1">
         <f t="array" ref="F17">_xlfn.IFS(D17&lt;0, "U", D17&gt;0, "F", D17=0, "-")</f>
         <v>-</v>
       </c>
@@ -12619,54 +12719,53 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="133" t="s">
+      <c r="A18" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="137">
-        <f>'Forecast Assumptions'!B26/3</f>
-        <v>30000</v>
-      </c>
-      <c r="C18" s="137">
+      <c r="B18" s="132">
+        <v>31000</v>
+      </c>
+      <c r="C18" s="132">
         <f>'2026 Forecast'!B25/3</f>
         <v>30000</v>
       </c>
-      <c r="D18" s="137">
-        <f>B18-C18</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="138">
-        <f>B18/C18-1</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="136" t="str" cm="1">
+      <c r="D18" s="132">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="E18" s="133">
+        <f t="shared" si="2"/>
+        <v>3.3333333333333437E-2</v>
+      </c>
+      <c r="F18" s="131" t="str" cm="1">
         <f t="array" ref="F18">_xlfn.IFS(D18&lt;0, "U", D18&gt;0, "F", D18=0, "-")</f>
-        <v>-</v>
+        <v>F</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="133" t="s">
+      <c r="A19" s="128" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="137">
+      <c r="B19" s="132">
         <f>'Forecast Assumptions'!B27/3</f>
         <v>25000</v>
       </c>
-      <c r="C19" s="137">
+      <c r="C19" s="132">
         <f>'2026 Forecast'!B26/3</f>
         <v>25000</v>
       </c>
-      <c r="D19" s="137">
-        <f>B19-C19</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="138">
-        <f>B19/C19-1</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="136" t="str" cm="1">
+      <c r="D19" s="132">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="133">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="131" t="str" cm="1">
         <f t="array" ref="F19">_xlfn.IFS(D19&lt;0, "U", D19&gt;0, "F", D19=0, "-")</f>
         <v>-</v>
       </c>
@@ -12675,26 +12774,26 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="151" t="s">
+      <c r="A20" s="128" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="156">
+      <c r="B20" s="132">
         <f>'Forecast Assumptions'!B28/3</f>
         <v>19000</v>
       </c>
-      <c r="C20" s="156">
+      <c r="C20" s="132">
         <f>'2026 Forecast'!B27/3</f>
         <v>19000</v>
       </c>
-      <c r="D20" s="156">
-        <f>B20-C20</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="157">
-        <f>B20/C20-1</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="158" t="str" cm="1">
+      <c r="D20" s="132">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="133">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="131" t="str" cm="1">
         <f t="array" ref="F20">_xlfn.IFS(D20&lt;0, "U", D20&gt;0, "F", D20=0, "-")</f>
         <v>-</v>
       </c>
@@ -12703,54 +12802,54 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="143" t="s">
+      <c r="A21" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="159">
+      <c r="B21" s="147">
         <f>SUM(B18:B20)</f>
-        <v>74000</v>
-      </c>
-      <c r="C21" s="159">
+        <v>75000</v>
+      </c>
+      <c r="C21" s="147">
         <f>'2026 Forecast'!B28/3</f>
         <v>74000</v>
       </c>
-      <c r="D21" s="159">
-        <f>B21-C21</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="162">
-        <f>B21/C21-1</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="161" t="str" cm="1">
+      <c r="D21" s="147">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="E21" s="150">
+        <f t="shared" si="2"/>
+        <v>1.3513513513513598E-2</v>
+      </c>
+      <c r="F21" s="149" t="str" cm="1">
         <f t="array" ref="F21">_xlfn.IFS(D21&lt;0, "U", D21&gt;0, "F", D21=0, "-")</f>
-        <v>-</v>
+        <v>F</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="164" t="s">
+      <c r="A22" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="165">
+      <c r="B22" s="153">
         <f>B16-B21</f>
-        <v>31213.849999999991</v>
-      </c>
-      <c r="C22" s="165">
+        <v>30213.849999999991</v>
+      </c>
+      <c r="C22" s="153">
         <f>C16-C21</f>
         <v>29978.735583333342</v>
       </c>
-      <c r="D22" s="165">
-        <f>B22-C22</f>
-        <v>1235.114416666649</v>
-      </c>
-      <c r="E22" s="166">
-        <f>B22/C22-1</f>
-        <v>4.1199683463411629E-2</v>
-      </c>
-      <c r="F22" s="167" t="str" cm="1">
+      <c r="D22" s="153">
+        <f t="shared" si="1"/>
+        <v>235.11441666664905</v>
+      </c>
+      <c r="E22" s="154">
+        <f t="shared" si="2"/>
+        <v>7.842706241331987E-3</v>
+      </c>
+      <c r="F22" s="155" t="str" cm="1">
         <f t="array" ref="F22">_xlfn.IFS(D22&lt;0, "U", D22&gt;0, "F", D22=0, "-")</f>
         <v>F</v>
       </c>
@@ -12759,368 +12858,368 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="133" t="s">
+      <c r="A23" s="128" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="138">
+      <c r="B23" s="133">
         <f>B22/B14</f>
-        <v>0.20766938002934018</v>
-      </c>
-      <c r="C23" s="138">
+        <v>0.2010162635432502</v>
+      </c>
+      <c r="C23" s="133">
         <f>C22/C14</f>
         <v>0.20182121652667054</v>
       </c>
-      <c r="D23" s="138">
-        <f>B23-C23</f>
-        <v>5.8481635026696455E-3</v>
-      </c>
-      <c r="E23" s="138">
-        <f>B23/C23-1</f>
-        <v>2.8976951003051754E-2</v>
-      </c>
-      <c r="F23" s="136" t="str" cm="1">
+      <c r="D23" s="133">
+        <f t="shared" si="1"/>
+        <v>-8.0495298342034283E-4</v>
+      </c>
+      <c r="E23" s="133">
+        <f t="shared" si="2"/>
+        <v>-3.9884458000676304E-3</v>
+      </c>
+      <c r="F23" s="131" t="str" cm="1">
         <f t="array" ref="F23">IFERROR(_xlfn.IFS(D23&lt;0, "U", D23&gt;0, "F", D23=0, "-"), "-")</f>
-        <v>F</v>
+        <v>U</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="170"/>
+      <c r="A25" s="158"/>
     </row>
     <row r="27" spans="1:8" ht="17" x14ac:dyDescent="0.4">
-      <c r="A27" s="172" t="s">
+      <c r="A27" s="160" t="s">
         <v>658</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="173" t="s">
+      <c r="A29" s="161" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="173" t="s">
+      <c r="B29" s="161" t="s">
         <v>283</v>
       </c>
-      <c r="C29" s="173" t="s">
+      <c r="C29" s="161" t="s">
         <v>659</v>
       </c>
-      <c r="D29" s="173" t="s">
+      <c r="D29" s="161" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="129" t="s">
+      <c r="A30" s="124" t="s">
         <v>193</v>
       </c>
-      <c r="B30" s="174">
+      <c r="B30" s="162">
         <v>41</v>
       </c>
-      <c r="C30" s="129">
+      <c r="C30" s="124">
         <f>IFERROR(B30-_xlfn.XLOOKUP("Active Customers",'KPI Tracker'!$A$4:$A$16,'KPI Tracker'!$B$4:$B$16),"—")</f>
         <v>2</v>
       </c>
-      <c r="D30" s="129" t="s">
+      <c r="D30" s="124" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="129" t="s">
+      <c r="A31" s="124" t="s">
         <v>194</v>
       </c>
-      <c r="B31" s="174">
+      <c r="B31" s="162">
         <v>53</v>
       </c>
-      <c r="C31" s="129" t="str">
+      <c r="C31" s="124" t="str">
         <f>IFERROR(B31-_xlfn.XLOOKUP("Active Subscriptions",'KPI Tracker'!$A$4:$A$16,'KPI Tracker'!$B$4:$B$16),"—")</f>
         <v>—</v>
       </c>
-      <c r="D31" s="129" t="s">
+      <c r="D31" s="124" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="129" t="s">
+      <c r="A32" s="124" t="s">
         <v>616</v>
       </c>
-      <c r="B32" s="137">
+      <c r="B32" s="132">
         <f>B9/B30</f>
         <v>3665.9878048780488</v>
       </c>
-      <c r="C32" s="137">
+      <c r="C32" s="132">
         <f>IFERROR(B32-_xlfn.XLOOKUP("ARPA",'KPI Tracker'!$A$4:$A$16,'KPI Tracker'!$B$4:$B$16),"—")</f>
         <v>-46.307066916822805</v>
       </c>
-      <c r="D32" s="129" t="s">
+      <c r="D32" s="124" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="129" t="s">
+      <c r="A33" s="124" t="s">
         <v>618</v>
       </c>
-      <c r="B33" s="175">
+      <c r="B33" s="163">
         <f>B17</f>
         <v>0.7</v>
       </c>
-      <c r="C33" s="175">
+      <c r="C33" s="163">
         <f>IFERROR(B33-_xlfn.XLOOKUP("Gross Margin",'KPI Tracker'!$A$4:$A$16,'KPI Tracker'!$B$4:$B$16),"—")</f>
         <v>0</v>
       </c>
-      <c r="D33" s="129" t="s">
+      <c r="D33" s="124" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="129" t="s">
+      <c r="A34" s="124" t="s">
         <v>620</v>
       </c>
-      <c r="B34" s="175">
+      <c r="B34" s="163">
         <f>Retention!AA6</f>
         <v>0.99610819735501566</v>
       </c>
-      <c r="C34" s="175">
+      <c r="C34" s="163">
         <f>IFERROR(B34-_xlfn.XLOOKUP("GRR",'KPI Tracker'!$A$4:$A$16,'KPI Tracker'!$B$4:$B$16),"—")</f>
         <v>-3.8918026449843435E-3</v>
       </c>
-      <c r="D34" s="129" t="s">
+      <c r="D34" s="124" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="129" t="s">
+      <c r="A35" s="124" t="s">
         <v>622</v>
       </c>
-      <c r="B35" s="175">
+      <c r="B35" s="163">
         <f>Retention!AA7</f>
         <v>0.99610819735501566</v>
       </c>
-      <c r="C35" s="175">
+      <c r="C35" s="163">
         <f>IFERROR(B35-_xlfn.XLOOKUP("NRR",'KPI Tracker'!$A$4:$A$16,'KPI Tracker'!$B$4:$B$16),"—")</f>
         <v>-3.8918026449843435E-3</v>
       </c>
-      <c r="D35" s="129" t="s">
+      <c r="D35" s="124" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="129" t="s">
+      <c r="A36" s="124" t="s">
         <v>623</v>
       </c>
-      <c r="B36" s="129">
+      <c r="B36" s="124">
         <f>IFERROR(IF((B6+B7)=0,"N/A — no losses",(B4+B5)/(B6+B7)),"N/A")</f>
         <v>10.303030303030303</v>
       </c>
-      <c r="C36" s="129" t="str">
+      <c r="C36" s="124">
         <f>IFERROR(IF(ISNUMBER(B36),B36-_xlfn.XLOOKUP("Quick Ratio",'KPI Tracker'!$A$4:$A$16,'KPI Tracker'!$B$4:$B$16),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="D36" s="129" t="s">
+        <v>10.303030303030303</v>
+      </c>
+      <c r="D36" s="124" t="s">
         <v>662</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="129" t="s">
+      <c r="A37" s="124" t="s">
         <v>625</v>
       </c>
-      <c r="B37" s="176">
+      <c r="B37" s="164">
         <f>B18</f>
-        <v>30000</v>
-      </c>
-      <c r="C37" s="176">
+        <v>31000</v>
+      </c>
+      <c r="C37" s="164">
         <f>IFERROR(B37-_xlfn.XLOOKUP("S&amp;M (actual)",'KPI Tracker'!$A$4:$A$16,'KPI Tracker'!$B$4:$B$16),"—")</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="129" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D37" s="124" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="129" t="s">
+      <c r="A38" s="124" t="s">
         <v>627</v>
       </c>
-      <c r="B38" s="176">
+      <c r="B38" s="164">
         <f>IFERROR(IF(B39=0,"—",B37/B39),"—")</f>
-        <v>15000</v>
-      </c>
-      <c r="C38" s="176">
+        <v>15500</v>
+      </c>
+      <c r="C38" s="164">
         <f>IFERROR(IF(ISNUMBER(B38),B38-_xlfn.XLOOKUP("CAC — monthly",'KPI Tracker'!$A$4:$A$16,'KPI Tracker'!$B$4:$B$16),"—"),"—")</f>
-        <v>-15000</v>
-      </c>
-      <c r="D38" s="129" t="s">
+        <v>-14500</v>
+      </c>
+      <c r="D38" s="124" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="177" t="s">
+      <c r="A39" s="165" t="s">
         <v>665</v>
       </c>
-      <c r="B39" s="188">
+      <c r="B39" s="175">
         <v>2</v>
       </c>
-      <c r="C39" s="129" t="s">
+      <c r="C39" s="124" t="s">
         <v>629</v>
       </c>
-      <c r="D39" s="177" t="s">
+      <c r="D39" s="165" t="s">
         <v>666</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="129" t="s">
+      <c r="A40" s="124" t="s">
         <v>660</v>
       </c>
-      <c r="B40" s="176">
+      <c r="B40" s="164">
         <f>IFERROR(IF(('Jan 2026 A vs F '!B46/'Jan 2026 A vs F '!B47+B39)=0,"—",('Jan 2026 A vs F '!B46+B37)/('Jan 2026 A vs F '!B46/'Jan 2026 A vs F '!B47+B39)),"—")</f>
-        <v>20000</v>
-      </c>
-      <c r="C40" s="129" t="s">
+        <v>20333.333333333332</v>
+      </c>
+      <c r="C40" s="124" t="s">
         <v>629</v>
       </c>
-      <c r="D40" s="129" t="s">
+      <c r="D40" s="124" t="s">
         <v>664</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="129" t="s">
+      <c r="A41" s="124" t="s">
         <v>628</v>
       </c>
-      <c r="B41" s="129" t="s">
+      <c r="B41" s="124" t="s">
         <v>629</v>
       </c>
-      <c r="C41" s="129" t="s">
+      <c r="C41" s="124" t="s">
         <v>629</v>
       </c>
-      <c r="D41" s="129" t="s">
+      <c r="D41" s="124" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="129" t="s">
+      <c r="A42" s="124" t="s">
         <v>631</v>
       </c>
-      <c r="B42" s="129" t="s">
+      <c r="B42" s="124" t="s">
         <v>629</v>
       </c>
-      <c r="C42" s="129" t="s">
+      <c r="C42" s="124" t="s">
         <v>629</v>
       </c>
-      <c r="D42" s="129" t="s">
+      <c r="D42" s="124" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="129" t="s">
+      <c r="A43" s="124" t="s">
         <v>632</v>
       </c>
-      <c r="B43" s="129" t="s">
+      <c r="B43" s="124" t="s">
         <v>629</v>
       </c>
-      <c r="C43" s="129" t="s">
+      <c r="C43" s="124" t="s">
         <v>629</v>
       </c>
-      <c r="D43" s="129" t="s">
+      <c r="D43" s="124" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="178" t="s">
+      <c r="A44" s="166" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="178" t="s">
+      <c r="A45" s="166" t="s">
         <v>667</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="178" t="s">
+      <c r="A47" s="166" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="178" t="s">
+      <c r="A48" s="166" t="s">
         <v>636</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A51" s="179" t="s">
+      <c r="A51" s="167" t="s">
         <v>638</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="173" t="s">
+      <c r="A53" s="161" t="s">
         <v>4</v>
       </c>
-      <c r="B53" s="173" t="s">
+      <c r="B53" s="161" t="s">
         <v>639</v>
       </c>
-      <c r="C53" s="173" t="s">
+      <c r="C53" s="161" t="s">
         <v>668</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="129" t="s">
+      <c r="A54" s="124" t="s">
         <v>616</v>
       </c>
-      <c r="B54" s="137">
+      <c r="B54" s="132">
         <f>B32</f>
         <v>3665.9878048780488</v>
       </c>
-      <c r="C54" s="137">
+      <c r="C54" s="132">
         <f>B9/B30</f>
         <v>3665.9878048780488</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="129" t="s">
+      <c r="A55" s="124" t="s">
         <v>620</v>
       </c>
-      <c r="B55" s="175">
+      <c r="B55" s="163">
         <f>B34</f>
         <v>0.99610819735501566</v>
       </c>
-      <c r="C55" s="175">
+      <c r="C55" s="163">
         <f>Retention!AA6</f>
         <v>0.99610819735501566</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="129" t="s">
+      <c r="A56" s="124" t="s">
         <v>622</v>
       </c>
-      <c r="B56" s="175">
+      <c r="B56" s="163">
         <f>B35</f>
         <v>0.99610819735501566</v>
       </c>
-      <c r="C56" s="175">
+      <c r="C56" s="163">
         <f>Retention!AA7</f>
         <v>0.99610819735501566</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="129" t="s">
+      <c r="A57" s="124" t="s">
         <v>623</v>
       </c>
-      <c r="B57" s="129">
+      <c r="B57" s="124">
         <f>B36</f>
         <v>10.303030303030303</v>
       </c>
-      <c r="C57" s="129">
+      <c r="C57" s="124">
         <f>IFERROR(IF((B6+B7)=0,"N/A — no losses",(B4+B5)/(B6+B7)),"N/A")</f>
         <v>10.303030303030303</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="129" t="s">
+      <c r="A58" s="124" t="s">
         <v>640</v>
       </c>
-      <c r="B58" s="176">
+      <c r="B58" s="164">
         <f>B38</f>
-        <v>15000</v>
-      </c>
-      <c r="C58" s="176">
+        <v>15500</v>
+      </c>
+      <c r="C58" s="164">
         <f>IFERROR(IF(B39=0,"—",B37/B39),"—")</f>
-        <v>15000</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="130" t="s">
+      <c r="A60" s="125" t="s">
         <v>611</v>
       </c>
     </row>
@@ -13171,17 +13270,14 @@
       <c r="A3" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="180" t="str">
-        <f>TEXT(DATE(2026,1,1),"mmm-yy")</f>
-        <v>Jan-26</v>
-      </c>
-      <c r="C3" s="180" t="str">
-        <f>TEXT(DATE(2026,2,1),"mmm-yy")</f>
-        <v>Feb-26</v>
-      </c>
-      <c r="D3" s="180" t="str">
-        <f>TEXT(DATE(2026,3,1),"mmm-yy")</f>
-        <v>Mar-26</v>
+      <c r="B3" s="184" t="s">
+        <v>674</v>
+      </c>
+      <c r="C3" s="184" t="s">
+        <v>675</v>
+      </c>
+      <c r="D3" s="184" t="s">
+        <v>676</v>
       </c>
       <c r="E3" s="118" t="s">
         <v>81</v>
@@ -13195,7 +13291,7 @@
         <f>'Jan 2026 A vs F '!B9</f>
         <v>144779.5</v>
       </c>
-      <c r="C4" s="137">
+      <c r="C4" s="132">
         <f>'Feb 2026 A vs F'!B9</f>
         <v>150305.5</v>
       </c>
@@ -13209,7 +13305,7 @@
         <f>'Jan 2026 A vs F '!B39</f>
         <v>39</v>
       </c>
-      <c r="C5" s="181">
+      <c r="C5" s="168">
         <f>'Feb 2026 A vs F'!B30</f>
         <v>41</v>
       </c>
@@ -13223,7 +13319,7 @@
         <f>'Jan 2026 A vs F '!B41</f>
         <v>3712.2948717948716</v>
       </c>
-      <c r="C6" s="137">
+      <c r="C6" s="132">
         <f>'Feb 2026 A vs F'!B32</f>
         <v>3665.9878048780488</v>
       </c>
@@ -13237,7 +13333,7 @@
         <f>'Jan 2026 A vs F '!B42</f>
         <v>0.7</v>
       </c>
-      <c r="C7" s="175">
+      <c r="C7" s="163">
         <f>'Feb 2026 A vs F'!B33</f>
         <v>0.7</v>
       </c>
@@ -13251,7 +13347,7 @@
         <f>'Jan 2026 A vs F '!B43</f>
         <v>1</v>
       </c>
-      <c r="C8" s="175">
+      <c r="C8" s="163">
         <f>'Feb 2026 A vs F'!B34</f>
         <v>0.99610819735501566</v>
       </c>
@@ -13265,7 +13361,7 @@
         <f>'Jan 2026 A vs F '!B44</f>
         <v>1</v>
       </c>
-      <c r="C9" s="175">
+      <c r="C9" s="163">
         <f>'Feb 2026 A vs F'!B35</f>
         <v>0.99610819735501566</v>
       </c>
@@ -13275,11 +13371,7 @@
       <c r="A10" t="s">
         <v>623</v>
       </c>
-      <c r="B10" t="str">
-        <f>'Jan 2026 A vs F '!B45</f>
-        <v>N/A — no losses</v>
-      </c>
-      <c r="C10" s="129">
+      <c r="C10" s="124">
         <f>'Feb 2026 A vs F'!B36</f>
         <v>10.303030303030303</v>
       </c>
@@ -13293,9 +13385,9 @@
         <f>'Jan 2026 A vs F '!B46</f>
         <v>30000</v>
       </c>
-      <c r="C11" s="176">
+      <c r="C11" s="164">
         <f>'Feb 2026 A vs F'!B37</f>
-        <v>30000</v>
+        <v>31000</v>
       </c>
       <c r="E11" s="119"/>
     </row>
@@ -13307,9 +13399,9 @@
         <f>'Jan 2026 A vs F '!B47</f>
         <v>30000</v>
       </c>
-      <c r="C12" s="176">
+      <c r="C12" s="164">
         <f>'Feb 2026 A vs F'!B38</f>
-        <v>15000</v>
+        <v>15500</v>
       </c>
       <c r="E12" s="119"/>
     </row>
@@ -13317,15 +13409,11 @@
       <c r="A13" s="119" t="s">
         <v>643</v>
       </c>
-      <c r="B13" s="121" t="s">
-        <v>629</v>
-      </c>
-      <c r="C13" s="121" t="s">
-        <v>629</v>
-      </c>
-      <c r="D13" s="121" t="s">
-        <v>629</v>
-      </c>
+      <c r="B13" s="121">
+        <v>0</v>
+      </c>
+      <c r="C13" s="121"/>
+      <c r="D13" s="121"/>
       <c r="E13" s="122" t="s">
         <v>644</v>
       </c>
@@ -13334,15 +13422,11 @@
       <c r="A14" s="119" t="s">
         <v>628</v>
       </c>
-      <c r="B14" s="121" t="s">
-        <v>629</v>
-      </c>
-      <c r="C14" s="121" t="s">
-        <v>629</v>
-      </c>
-      <c r="D14" s="121" t="s">
-        <v>629</v>
-      </c>
+      <c r="B14" s="121">
+        <v>0</v>
+      </c>
+      <c r="C14" s="121"/>
+      <c r="D14" s="121"/>
       <c r="E14" s="122" t="s">
         <v>644</v>
       </c>
@@ -13351,15 +13435,11 @@
       <c r="A15" s="119" t="s">
         <v>631</v>
       </c>
-      <c r="B15" s="121" t="s">
-        <v>629</v>
-      </c>
-      <c r="C15" s="121" t="s">
-        <v>629</v>
-      </c>
-      <c r="D15" s="121" t="s">
-        <v>629</v>
-      </c>
+      <c r="B15" s="121">
+        <v>0</v>
+      </c>
+      <c r="C15" s="121"/>
+      <c r="D15" s="121"/>
       <c r="E15" s="122" t="s">
         <v>644</v>
       </c>
@@ -13368,25 +13448,21 @@
       <c r="A16" s="119" t="s">
         <v>632</v>
       </c>
-      <c r="B16" s="121" t="s">
-        <v>629</v>
-      </c>
-      <c r="C16" s="121" t="s">
-        <v>629</v>
-      </c>
-      <c r="D16" s="121" t="s">
-        <v>629</v>
-      </c>
+      <c r="B16" s="121">
+        <v>0</v>
+      </c>
+      <c r="C16" s="121"/>
+      <c r="D16" s="121"/>
       <c r="E16" s="122" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="125" t="s">
+      <c r="A18" s="176" t="s">
         <v>645</v>
       </c>
-      <c r="B18" s="125"/>
-      <c r="C18" s="125"/>
+      <c r="B18" s="176"/>
+      <c r="C18" s="176"/>
       <c r="D18" s="123"/>
       <c r="E18" s="123"/>
     </row>
@@ -13395,11 +13471,14 @@
     <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51A400A-F6A7-4884-99EF-FD343C8B71C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51A400A-F6A7-4884-99EF-FD343C8B71C2}">
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
@@ -13524,7 +13603,7 @@
         <f>'Jan 2026 A vs F '!C7</f>
         <v>953.79666666666662</v>
       </c>
-      <c r="E6" s="182">
+      <c r="E6" s="169">
         <f>D6-C6</f>
         <v>953.79666666666662</v>
       </c>
@@ -13570,150 +13649,150 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="183" t="str">
-        <f>TEXT(DATE(2026,2,1),"mmm-yy")</f>
+      <c r="A9" s="172" t="str">
+        <f t="shared" ref="A9:A15" si="0">TEXT(DATE(2026,2,1),"mmm-yy")</f>
         <v>Feb-26</v>
       </c>
-      <c r="B9" s="186" t="s">
+      <c r="B9" s="171" t="s">
+        <v>650</v>
+      </c>
+      <c r="C9" s="174">
+        <f>'Feb 2026 A vs F'!B4</f>
+        <v>6120</v>
+      </c>
+      <c r="D9" s="174">
+        <f>'Feb 2026 A vs F'!C4</f>
+        <v>4000</v>
+      </c>
+      <c r="E9" s="174">
+        <f>C9-D9</f>
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="170" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb-26</v>
+      </c>
+      <c r="B10" s="173" t="s">
+        <v>651</v>
+      </c>
+      <c r="C10" s="169">
+        <f>'Feb 2026 A vs F'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="169">
+        <f>'Feb 2026 A vs F'!C5</f>
+        <v>715.34749999999997</v>
+      </c>
+      <c r="E10" s="169">
+        <f>C10-D10</f>
+        <v>-715.34749999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="172" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb-26</v>
+      </c>
+      <c r="B11" s="171" t="s">
+        <v>652</v>
+      </c>
+      <c r="C11" s="174">
+        <f>'Feb 2026 A vs F'!B6</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="174">
+        <f>'Feb 2026 A vs F'!C6</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="174">
+        <f>D11-C11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="170" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb-26</v>
+      </c>
+      <c r="B12" s="173" t="s">
+        <v>653</v>
+      </c>
+      <c r="C12" s="169">
+        <f>'Feb 2026 A vs F'!B7</f>
+        <v>594</v>
+      </c>
+      <c r="D12" s="169">
+        <f>'Feb 2026 A vs F'!C7</f>
+        <v>953.79666666666662</v>
+      </c>
+      <c r="E12" s="169">
+        <f>D12-C12</f>
+        <v>359.79666666666662</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="172" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb-26</v>
+      </c>
+      <c r="B13" s="171" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="174">
+        <f>'Feb 2026 A vs F'!B8</f>
+        <v>5526</v>
+      </c>
+      <c r="D13" s="174">
+        <f>'Feb 2026 A vs F'!C8</f>
+        <v>3761.5508333333332</v>
+      </c>
+      <c r="E13" s="174">
+        <f>C13-D13</f>
+        <v>1764.4491666666668</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="170" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb-26</v>
+      </c>
+      <c r="B14" s="173" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="169">
+        <f>'Feb 2026 A vs F'!B9</f>
+        <v>150305.5</v>
+      </c>
+      <c r="D14" s="169">
+        <f>'Feb 2026 A vs F'!C9</f>
+        <v>148541.05083333334</v>
+      </c>
+      <c r="E14" s="169">
+        <f>C14-D14</f>
+        <v>1764.4491666666581</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="181" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb-26</v>
+      </c>
+      <c r="B15" s="182" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="182">
+      <c r="C15" s="183">
         <f>'Feb 2026 A vs F'!B3</f>
         <v>144779.5</v>
       </c>
-      <c r="D9" s="182">
+      <c r="D15" s="183">
         <f>'Feb 2026 A vs F'!C3</f>
         <v>144779.5</v>
       </c>
-      <c r="E9" s="182">
-        <f>C9-D9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="185" t="str">
-        <f>TEXT(DATE(2026,2,1),"mmm-yy")</f>
-        <v>Feb-26</v>
-      </c>
-      <c r="B10" s="184" t="s">
-        <v>650</v>
-      </c>
-      <c r="C10" s="187">
-        <f>'Feb 2026 A vs F'!B4</f>
-        <v>6120</v>
-      </c>
-      <c r="D10" s="187">
-        <f>'Feb 2026 A vs F'!C4</f>
-        <v>4000</v>
-      </c>
-      <c r="E10" s="187">
-        <f>C10-D10</f>
-        <v>2120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="183" t="str">
-        <f>TEXT(DATE(2026,2,1),"mmm-yy")</f>
-        <v>Feb-26</v>
-      </c>
-      <c r="B11" s="186" t="s">
-        <v>651</v>
-      </c>
-      <c r="C11" s="182">
-        <f>'Feb 2026 A vs F'!B5</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="182">
-        <f>'Feb 2026 A vs F'!C5</f>
-        <v>715.34749999999997</v>
-      </c>
-      <c r="E11" s="182">
-        <f>C11-D11</f>
-        <v>-715.34749999999997</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="185" t="str">
-        <f>TEXT(DATE(2026,2,1),"mmm-yy")</f>
-        <v>Feb-26</v>
-      </c>
-      <c r="B12" s="184" t="s">
-        <v>652</v>
-      </c>
-      <c r="C12" s="187">
-        <f>'Feb 2026 A vs F'!B6</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="187">
-        <f>'Feb 2026 A vs F'!C6</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="187">
-        <f>D12-C12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="183" t="str">
-        <f>TEXT(DATE(2026,2,1),"mmm-yy")</f>
-        <v>Feb-26</v>
-      </c>
-      <c r="B13" s="186" t="s">
-        <v>653</v>
-      </c>
-      <c r="C13" s="182">
-        <f>'Feb 2026 A vs F'!B7</f>
-        <v>594</v>
-      </c>
-      <c r="D13" s="182">
-        <f>'Feb 2026 A vs F'!C7</f>
-        <v>953.79666666666662</v>
-      </c>
-      <c r="E13" s="182">
-        <f>D13-C13</f>
-        <v>359.79666666666662</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="185" t="str">
-        <f>TEXT(DATE(2026,2,1),"mmm-yy")</f>
-        <v>Feb-26</v>
-      </c>
-      <c r="B14" s="184" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="187">
-        <f>'Feb 2026 A vs F'!B8</f>
-        <v>5526</v>
-      </c>
-      <c r="D14" s="187">
-        <f>'Feb 2026 A vs F'!C8</f>
-        <v>3761.5508333333332</v>
-      </c>
-      <c r="E14" s="187">
-        <f>C14-D14</f>
-        <v>1764.4491666666668</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="183" t="str">
-        <f>TEXT(DATE(2026,2,1),"mmm-yy")</f>
-        <v>Feb-26</v>
-      </c>
-      <c r="B15" s="186" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="182">
-        <f>'Feb 2026 A vs F'!B9</f>
-        <v>150305.5</v>
-      </c>
-      <c r="D15" s="182">
-        <f>'Feb 2026 A vs F'!C9</f>
-        <v>148541.05083333334</v>
-      </c>
-      <c r="E15" s="182">
+      <c r="E15" s="183">
         <f>C15-D15</f>
-        <v>1764.4491666666581</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="9:9" x14ac:dyDescent="0.35">
@@ -13723,9 +13802,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
